--- a/02_APriori_PBPK_Workflow/Configurations/ModelParameters.xlsx
+++ b/02_APriori_PBPK_Workflow/Configurations/ModelParameters.xlsx
@@ -1636,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.299</v>
+        <v>0.000299</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -1751,7 +1751,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.299</v>
+        <v>0.000299</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
